--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105351_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105351_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.877</v>
+        <v>0.9409</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8718</v>
+        <v>3.9951</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.9948</v>
+        <v>-3.0541</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0891</v>
+        <v>2.2015</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0915</v>
+        <v>0.147</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9977</v>
+        <v>2.0545</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4232</v>
+        <v>4.633</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2946</v>
+        <v>2.39</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1285</v>
+        <v>2.243</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.334</v>
+        <v>-2.4315</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2031</v>
+        <v>-2.243</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1309</v>
+        <v>-0.1885</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6923</v>
+        <v>-0.6885</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3737</v>
+        <v>-0.4212</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4746</v>
+        <v>-0.5724</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1009</v>
+        <v>0.1513</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W2" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,58 +653,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.158</v>
+        <v>0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5113</v>
+        <v>0.4857</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3533</v>
+        <v>-0.3657</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1111</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6402</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5291</v>
+        <v>-0.5523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8862</v>
+        <v>0.8925</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8124</v>
+        <v>0.8184</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7751</v>
+        <v>-0.8234</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1722</v>
+        <v>-0.1969</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6029</v>
+        <v>-0.6264</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1839</v>
+        <v>-0.1786</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3749</v>
+        <v>-0.4068</v>
       </c>
       <c r="U3" t="n">
-        <v>0.191</v>
+        <v>0.2282</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>-0.6094000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.5596</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.7792</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.1324</v>
+      </c>
+      <c r="I4" t="n">
         <v>-0.6468</v>
       </c>
-      <c r="E4" t="n">
-        <v>-0.6079</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-0.0388</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1.836</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-1.1629</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.6731</v>
-      </c>
       <c r="J4" t="n">
-        <v>-1.6657</v>
+        <v>-1.5998</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8244</v>
+        <v>-0.7914</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8413</v>
+        <v>-0.8084</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1702</v>
+        <v>-0.1793</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3385</v>
+        <v>-0.341</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1683</v>
+        <v>0.1617</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0277</v>
+        <v>0.0091</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0192</v>
+        <v>-0.0417</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0469</v>
+        <v>0.0509</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9308</v>
+        <v>0.9312</v>
       </c>
       <c r="W4" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1389</v>
+        <v>-1.2388</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6775</v>
+        <v>0.6217</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8164</v>
+        <v>-1.8606</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6629</v>
+        <v>-0.7149</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0363</v>
+        <v>-1.0753</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3735</v>
+        <v>0.3604</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1942</v>
+        <v>1.2346</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1523</v>
+        <v>0.1535</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0418</v>
+        <v>1.0811</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.857</v>
+        <v>-1.9495</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1886</v>
+        <v>-1.2288</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6684</v>
+        <v>-0.7207</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1304</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5167</v>
+        <v>-0.6129</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4254</v>
+        <v>0.4825</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3437</v>
+        <v>-1.4385</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0969</v>
+        <v>1.023</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4406</v>
+        <v>-2.4615</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6333</v>
+        <v>-0.7281</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3463</v>
+        <v>-0.4115</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.287</v>
+        <v>-0.3166</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7373</v>
+        <v>1.7858</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6925</v>
+        <v>1.705</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0449</v>
+        <v>0.0808</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3706</v>
+        <v>-2.5139</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0388</v>
+        <v>-2.1166</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3318</v>
+        <v>-0.3973</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3257</v>
+        <v>-0.3169</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6404</v>
+        <v>-0.7628</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3147</v>
+        <v>0.446</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7776</v>
+        <v>-1.7866</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0213</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7563</v>
+        <v>-0.7922</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8281</v>
+        <v>-1.7945</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9129</v>
+        <v>-0.9119</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9152</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.65</v>
+        <v>-0.5446</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7398</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0897</v>
+        <v>0.1615</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1781</v>
+        <v>-1.2498</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1732</v>
+        <v>-0.2058</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0049</v>
+        <v>-1.0441</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.411</v>
+        <v>-0.4512</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3713</v>
+        <v>-0.4499</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0397</v>
+        <v>-0.0013</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9008</v>
+        <v>-2.8784</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2483</v>
+        <v>-2.2066</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6525</v>
+        <v>-0.6718</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3062</v>
+        <v>-2.2635</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9613</v>
+        <v>-1.9602</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3449</v>
+        <v>-0.3032</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7916</v>
+        <v>-1.6902</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7736</v>
+        <v>-0.7402</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.018</v>
+        <v>-0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5732</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1877</v>
+        <v>-1.22</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6731</v>
+        <v>0.6468</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1406</v>
+        <v>-0.1526</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4566</v>
+        <v>-0.5164</v>
       </c>
       <c r="U8" t="n">
-        <v>0.316</v>
+        <v>0.3638</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1151,64 +1151,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2836</v>
+        <v>-3.1918</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2557</v>
+        <v>0.3928</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5392</v>
+        <v>-3.5846</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2757</v>
+        <v>-1.1803</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9429</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3328</v>
+        <v>-0.2696</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7046</v>
+        <v>2.9037</v>
       </c>
       <c r="K9" t="n">
-        <v>1.093</v>
+        <v>1.1794</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6116</v>
+        <v>1.7243</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.9802</v>
+        <v>-4.084</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0359</v>
+        <v>-2.0901</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9444</v>
+        <v>-1.9939</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.7067</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4338</v>
+        <v>-0.5177</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2513</v>
+        <v>-0.1891</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2924</v>
+        <v>0.3017</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2924</v>
+        <v>0.3017</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6167</v>
+        <v>-5.6357</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4755</v>
+        <v>-0.4335</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.1412</v>
+        <v>-5.2022</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6058</v>
+        <v>-3.5448</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0839</v>
+        <v>-1.982</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5218</v>
+        <v>-1.5628</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6728</v>
+        <v>-0.5221</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8943</v>
+        <v>-0.7444</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2215</v>
+        <v>0.2223</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.933</v>
+        <v>-3.0227</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1896</v>
+        <v>-1.2376</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7434</v>
+        <v>-1.7851</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0107</v>
+        <v>-0.0743</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1972</v>
+        <v>0.0887</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.208</v>
+        <v>-0.163</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6925</v>
+        <v>-2.705</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6925</v>
+        <v>-2.705</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9538</v>
+        <v>-6.021</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0397</v>
+        <v>1.0365</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.9935</v>
+        <v>-7.0575</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1488</v>
+        <v>-2.1703</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7263</v>
+        <v>-1.7391</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4225</v>
+        <v>-0.4311</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6621</v>
+        <v>1.7433</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1403</v>
+        <v>0.1805</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5218</v>
+        <v>1.5628</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.811</v>
+        <v>-3.9135</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8666</v>
+        <v>-1.9196</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9444</v>
+        <v>-1.9939</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8893</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.7067</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2669</v>
+        <v>-0.206</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.3772</v>
+        <v>-3.3969</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3772</v>
+        <v>-3.3969</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6041</v>
+        <v>-6.5371</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8644</v>
+        <v>-2.7481</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7397</v>
+        <v>-3.789</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3922</v>
+        <v>-2.2837</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.302</v>
+        <v>-2.1861</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0902</v>
+        <v>-0.0977</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0602</v>
+        <v>0.1302</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4373</v>
+        <v>-0.2841</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3772</v>
+        <v>0.4142</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.332</v>
+        <v>-2.4139</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8646</v>
+        <v>-1.902</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4674</v>
+        <v>-0.5119</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3581</v>
+        <v>-0.4042</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6429</v>
+        <v>-0.7341</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2848</v>
+        <v>0.3299</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0078</v>
+        <v>-2.0132</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6873</v>
+        <v>-6.6141</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4866</v>
+        <v>-2.3705</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2007</v>
+        <v>-4.2436</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.9059</v>
+        <v>-4.8024</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6034</v>
+        <v>-2.5993</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.3024</v>
+        <v>-2.203</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6681</v>
+        <v>-1.4946</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7398</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9283</v>
+        <v>-0.7885</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2378</v>
+        <v>-3.3078</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8637</v>
+        <v>-1.8932</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3742</v>
+        <v>-1.4146</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.846</v>
+        <v>-1.836</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6201</v>
+        <v>-0.6676</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8111</v>
+        <v>-0.8958</v>
       </c>
       <c r="U13" t="n">
-        <v>0.191</v>
+        <v>0.2282</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3002</v>
+        <v>2.3149</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-34.9183</v>
+        <v>-34.8905</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.251099999999999</v>
+        <v>-1.757999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-32.667</v>
+        <v>-33.1326</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.3947</v>
+        <v>-18.9911</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.3465</v>
+        <v>-14.1401</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.047800000000001</v>
+        <v>-4.8508</v>
       </c>
       <c r="J14" t="n">
-        <v>6.0992</v>
+        <v>7.4718</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7759</v>
+        <v>2.4545</v>
       </c>
       <c r="L14" t="n">
-        <v>4.323199999999999</v>
+        <v>5.0172</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.4936</v>
+        <v>-26.4625</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.1225</v>
+        <v>-16.5946</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.3713</v>
+        <v>-9.867900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.3073</v>
+        <v>-2.295</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.0763</v>
+        <v>-8.032499999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>5.769100000000001</v>
+        <v>5.737499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.0617</v>
+        <v>-4.4074</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.1668</v>
+        <v>-6.1285</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1048</v>
+        <v>1.7214</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.154500000000001</v>
+        <v>-9.197099999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>4.892799999999999</v>
+        <v>4.9315</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.0473</v>
+        <v>-14.1286</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,64 +1645,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.872</v>
+        <v>7.8681</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5607</v>
+        <v>7.5831</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3114</v>
+        <v>0.2849</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7981</v>
+        <v>6.721</v>
       </c>
       <c r="H15" t="n">
-        <v>3.409</v>
+        <v>3.356</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3891</v>
+        <v>3.3649</v>
       </c>
       <c r="J15" t="n">
-        <v>8.0177</v>
+        <v>8.097300000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>4.0957</v>
+        <v>4.1262</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9219</v>
+        <v>3.9711</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2196</v>
+        <v>-1.3763</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6868</v>
+        <v>-0.7702</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.6061</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S15" t="n">
-        <v>0.697</v>
+        <v>0.7667</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1417</v>
+        <v>-0.206</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8387</v>
+        <v>0.9727</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1728,64 +1728,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3789</v>
+        <v>6.422</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4291</v>
+        <v>5.5324</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9498</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>1.555</v>
+        <v>1.5444</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1082</v>
+        <v>1.046</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4468</v>
+        <v>0.4984</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8947</v>
+        <v>2.0122</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9478</v>
+        <v>0.9548</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9469</v>
+        <v>1.0574</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3397</v>
+        <v>-0.4678</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1604</v>
+        <v>0.0912</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5001</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R16" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4543</v>
+        <v>0.4772</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0878</v>
+        <v>0.0378</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3665</v>
+        <v>0.4394</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6004</v>
+        <v>4.6298</v>
       </c>
       <c r="W16" t="n">
-        <v>4.6004</v>
+        <v>4.6298</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1811,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7711</v>
+        <v>4.7833</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2034</v>
+        <v>4.2486</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5677</v>
+        <v>0.5346</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6017</v>
+        <v>4.5681</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1411</v>
+        <v>3.1097</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4606</v>
+        <v>1.4585</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5375</v>
+        <v>4.6007</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9787</v>
+        <v>3.0009</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5588</v>
+        <v>1.5998</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.0326</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1624</v>
+        <v>0.1088</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1414</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1694</v>
+        <v>0.2152</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1274</v>
+        <v>0.1069</v>
       </c>
       <c r="U17" t="n">
-        <v>0.042</v>
+        <v>0.1082</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1894,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3642</v>
+        <v>4.3975</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5054</v>
+        <v>3.5997</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8588</v>
+        <v>0.7978</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3534</v>
+        <v>3.3739</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1204</v>
+        <v>0.137</v>
       </c>
       <c r="I18" t="n">
-        <v>3.233</v>
+        <v>3.2369</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2336</v>
+        <v>4.4003</v>
       </c>
       <c r="K18" t="n">
-        <v>0.636</v>
+        <v>0.719</v>
       </c>
       <c r="L18" t="n">
-        <v>3.5976</v>
+        <v>3.6813</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8801</v>
+        <v>-1.0265</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.582</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3646</v>
+        <v>-0.4444</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3185</v>
+        <v>0.3351</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2667</v>
+        <v>-0.3416</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.6768</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1977,64 +1977,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2455</v>
+        <v>4.2459</v>
       </c>
       <c r="E19" t="n">
-        <v>4.1683</v>
+        <v>4.1987</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0772</v>
+        <v>0.0472</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4606</v>
+        <v>1.4077</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9444</v>
+        <v>1.9432</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4838</v>
+        <v>-0.5354</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3051</v>
+        <v>2.3606</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1205</v>
+        <v>2.1754</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1846</v>
+        <v>0.1853</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8445</v>
+        <v>-0.9529</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1761</v>
+        <v>-0.2322</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6684</v>
+        <v>-0.7207</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4002</v>
+        <v>0.4446</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.06</v>
+        <v>-0.0965</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4602</v>
+        <v>0.5411</v>
       </c>
       <c r="V19" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="W19" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.9025</v>
+        <v>2.8507</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7127</v>
+        <v>0.7052</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1898</v>
+        <v>2.1455</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6882</v>
+        <v>1.626</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3922</v>
+        <v>-0.4186</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0804</v>
+        <v>2.0446</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0865</v>
+        <v>1.1264</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7229</v>
+        <v>-0.6891</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8093</v>
+        <v>1.8155</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6017</v>
+        <v>0.4996</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3306</v>
+        <v>0.2705</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2711</v>
+        <v>0.2291</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5913</v>
+        <v>0.605</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.143</v>
+        <v>-0.1917</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7342</v>
+        <v>0.7967</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3923</v>
+        <v>0.3901</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3923</v>
+        <v>0.3901</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2296</v>
+        <v>2.1743</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9397</v>
+        <v>2.9365</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7101</v>
+        <v>-0.7623</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2872</v>
+        <v>-0.3537</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3853</v>
+        <v>0.3569</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6726</v>
+        <v>-0.7106</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0957</v>
+        <v>1.1402</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2355</v>
+        <v>1.2447</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1398</v>
+        <v>-0.1045</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.383</v>
+        <v>-1.4939</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8502</v>
+        <v>-0.8878</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.6061</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2091</v>
+        <v>0.2165</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.31</v>
+        <v>-0.3677</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5191</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6155</v>
+        <v>1.623</v>
       </c>
       <c r="W21" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.7907</v>
+        <v>1.7511</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0576</v>
+        <v>2.0432</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2669</v>
+        <v>-0.2921</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3024</v>
+        <v>0.2538</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5894</v>
+        <v>0.5703</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.287</v>
+        <v>-0.3166</v>
       </c>
       <c r="J22" t="n">
-        <v>0.745</v>
+        <v>0.789</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6408</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1477</v>
+        <v>0.1482</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4425</v>
+        <v>-0.5353</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0078</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4347</v>
+        <v>-0.4648</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S22" t="n">
-        <v>1.173</v>
+        <v>1.1892</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4664</v>
+        <v>0.4016</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7066</v>
+        <v>0.7876</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W22" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.345</v>
+        <v>1.3206</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0083</v>
+        <v>0.0033</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3367</v>
+        <v>1.3173</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7429</v>
+        <v>0.7091</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3694</v>
+        <v>0.3487</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3735</v>
+        <v>0.3604</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0708</v>
+        <v>0.0712</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0338</v>
+        <v>0.0341</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6721</v>
+        <v>0.6379</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3355</v>
+        <v>0.3146</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3365</v>
+        <v>0.3234</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1406</v>
+        <v>0.1526</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0625</v>
+        <v>-0.0678</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2031</v>
+        <v>0.2204</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1627</v>
+        <v>1.17</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8482</v>
+        <v>0.9055</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3146</v>
+        <v>0.2645</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8702</v>
+        <v>-0.881</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6571</v>
+        <v>-0.6385</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2131</v>
+        <v>-0.2425</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3454</v>
+        <v>0.4601</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1425</v>
+        <v>-0.0653</v>
       </c>
       <c r="L24" t="n">
-        <v>0.488</v>
+        <v>0.5254</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2157</v>
+        <v>-1.341</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5732</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.7678</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2308</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S24" t="n">
-        <v>0.256</v>
+        <v>0.2673</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2667</v>
+        <v>-0.3416</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6089</v>
       </c>
       <c r="V24" t="n">
-        <v>2.0078</v>
+        <v>2.0132</v>
       </c>
       <c r="W24" t="n">
-        <v>2.154</v>
+        <v>2.164</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2349</v>
+        <v>0.2365</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7048</v>
+        <v>0.749</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.47</v>
+        <v>-0.5125</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3756</v>
+        <v>-0.4103</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6019</v>
+        <v>1.5669</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9776</v>
+        <v>-1.9772</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2071</v>
+        <v>-0.1306</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4386</v>
+        <v>1.4493</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.6457</v>
+        <v>-1.5798</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1685</v>
+        <v>-0.2797</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1634</v>
+        <v>0.1176</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3318</v>
+        <v>-0.3973</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3797</v>
+        <v>0.4173</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3112</v>
+        <v>-0.3534</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.7706</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2558,67 +2558,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.225</v>
+        <v>-1.1819</v>
       </c>
       <c r="E26" t="n">
-        <v>0.529</v>
+        <v>0.6274</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7541</v>
+        <v>-1.8093</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4253</v>
+        <v>0.432</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7268</v>
+        <v>2.7628</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.3015</v>
+        <v>-2.3308</v>
       </c>
       <c r="J26" t="n">
-        <v>1.369</v>
+        <v>1.5351</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9039</v>
+        <v>3.0038</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.535</v>
+        <v>-1.4687</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9436</v>
+        <v>-1.1031</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1771</v>
+        <v>-0.241</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.7665</v>
+        <v>-0.8621</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4266</v>
+        <v>0.4681</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2247</v>
+        <v>-0.3012</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6513</v>
+        <v>0.7693</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.6155</v>
+        <v>-1.623</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.154</v>
+        <v>-2.164</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2641,67 +2641,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>36.07210000000001</v>
+        <v>36.0381</v>
       </c>
       <c r="E27" t="n">
-        <v>32.6672</v>
+        <v>33.1326</v>
       </c>
       <c r="F27" t="n">
-        <v>3.4049</v>
+        <v>2.9052</v>
       </c>
       <c r="G27" t="n">
-        <v>19.3946</v>
+        <v>18.991</v>
       </c>
       <c r="H27" t="n">
-        <v>14.3466</v>
+        <v>14.1404</v>
       </c>
       <c r="I27" t="n">
-        <v>5.047800000000001</v>
+        <v>4.8506</v>
       </c>
       <c r="J27" t="n">
-        <v>25.4939</v>
+        <v>26.4625</v>
       </c>
       <c r="K27" t="n">
-        <v>16.1224</v>
+        <v>16.5946</v>
       </c>
       <c r="L27" t="n">
-        <v>9.371199999999998</v>
+        <v>9.868099999999998</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.0992</v>
+        <v>-7.4716</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.7759</v>
+        <v>-2.4542</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.3233</v>
+        <v>-5.017200000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3077</v>
+        <v>2.295</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5.769</v>
+        <v>-5.7375</v>
       </c>
       <c r="R27" t="n">
-        <v>8.076599999999999</v>
+        <v>8.032499999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>5.2157</v>
+        <v>5.554799999999998</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.1049</v>
+        <v>-1.7212</v>
       </c>
       <c r="U27" t="n">
-        <v>6.3206</v>
+        <v>7.2759</v>
       </c>
       <c r="V27" t="n">
-        <v>9.154499999999999</v>
+        <v>9.197100000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>14.0473</v>
+        <v>14.1286</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.8928</v>
+        <v>-4.931600000000001</v>
       </c>
       <c r="Y27" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105351_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105351_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9409</v>
+        <v>0.837</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9951</v>
+        <v>3.7271</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0541</v>
+        <v>-2.8901</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2015</v>
+        <v>2.1315</v>
       </c>
       <c r="H2" t="n">
-        <v>0.147</v>
+        <v>0.1144</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0545</v>
+        <v>2.0171</v>
       </c>
       <c r="J2" t="n">
-        <v>4.633</v>
+        <v>4.4751</v>
       </c>
       <c r="K2" t="n">
-        <v>2.39</v>
+        <v>2.2863</v>
       </c>
       <c r="L2" t="n">
-        <v>2.243</v>
+        <v>2.1889</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4315</v>
+        <v>-2.3436</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.243</v>
+        <v>-2.1718</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1885</v>
+        <v>-0.1718</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6885</v>
+        <v>-0.7019</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R2" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4212</v>
+        <v>-0.4583</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5724</v>
+        <v>-0.6423</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1513</v>
+        <v>0.184</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W2" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,58 +653,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.12</v>
+        <v>0.1315</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4857</v>
+        <v>0.4355</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3657</v>
+        <v>-0.304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0772</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5523</v>
+        <v>-0.5403</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8925</v>
+        <v>0.8701</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8184</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8234</v>
+        <v>-0.793</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1969</v>
+        <v>-0.1795</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6264</v>
+        <v>-0.6135</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1786</v>
+        <v>-0.1796</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4068</v>
+        <v>-0.4346</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2282</v>
+        <v>0.255</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.607</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5596</v>
+        <v>-0.5904</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0498</v>
+        <v>-0.0165</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7792</v>
+        <v>-1.7693</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1324</v>
+        <v>-1.1231</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6468</v>
+        <v>-0.6462</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.5998</v>
+        <v>-1.5988</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7914</v>
+        <v>-0.7911</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1793</v>
+        <v>-0.1705</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.341</v>
+        <v>-0.3321</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0091</v>
+        <v>-0.0014</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0417</v>
+        <v>-0.0558</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0509</v>
+        <v>0.0543</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9312</v>
+        <v>0.9298</v>
       </c>
       <c r="W4" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2388</v>
+        <v>-1.1893</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6217</v>
+        <v>0.5258</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8606</v>
+        <v>-1.7151</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7149</v>
+        <v>-0.671</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0753</v>
+        <v>-1.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3604</v>
+        <v>0.3597</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2346</v>
+        <v>1.2085</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1535</v>
+        <v>0.1494</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0811</v>
+        <v>1.059</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9495</v>
+        <v>-1.8795</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2288</v>
+        <v>-1.1802</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7207</v>
+        <v>-0.6994</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1304</v>
+        <v>-0.1561</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6129</v>
+        <v>-0.6826</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4825</v>
+        <v>0.5266</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4385</v>
+        <v>-1.3546</v>
       </c>
       <c r="E6" t="n">
-        <v>1.023</v>
+        <v>0.8798</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4615</v>
+        <v>-2.2344</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7281</v>
+        <v>-0.6735</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4115</v>
+        <v>-0.368</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3166</v>
+        <v>-0.3055</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7858</v>
+        <v>1.7311</v>
       </c>
       <c r="K6" t="n">
-        <v>1.705</v>
+        <v>1.6603</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0808</v>
+        <v>0.0708</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5139</v>
+        <v>-2.4045</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1166</v>
+        <v>-2.0282</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3973</v>
+        <v>-0.3763</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3169</v>
+        <v>-0.3189</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7628</v>
+        <v>-0.8512</v>
       </c>
       <c r="U6" t="n">
-        <v>0.446</v>
+        <v>0.5323</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7866</v>
+        <v>-1.7898</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-1.0723</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7922</v>
+        <v>-0.7175</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7945</v>
+        <v>-1.773</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9119</v>
+        <v>-0.8921</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8809</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5446</v>
+        <v>-0.5665</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7081</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1615</v>
+        <v>0.1415</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2498</v>
+        <v>-1.2064</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2058</v>
+        <v>-0.184</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0441</v>
+        <v>-1.0224</v>
       </c>
       <c r="P7" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4512</v>
+        <v>-0.4848</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4499</v>
+        <v>-0.5057</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0013</v>
+        <v>0.021</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8784</v>
+        <v>-2.8227</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2066</v>
+        <v>-2.2606</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6718</v>
+        <v>-0.5621</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2635</v>
+        <v>-2.2273</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9602</v>
+        <v>-1.9169</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3032</v>
+        <v>-0.3104</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6902</v>
+        <v>-1.6978</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7402</v>
+        <v>-0.7413</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.95</v>
+        <v>-0.9565</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5732</v>
+        <v>-0.5295</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.22</v>
+        <v>-1.1757</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6468</v>
+        <v>0.6462</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1526</v>
+        <v>-0.163</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5164</v>
+        <v>-0.5628</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3638</v>
+        <v>0.3998</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1151,64 +1151,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1918</v>
+        <v>-3.2945</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3928</v>
+        <v>0.1346</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5846</v>
+        <v>-3.4291</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1803</v>
+        <v>-1.1899</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.9073</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2696</v>
+        <v>-0.2826</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9037</v>
+        <v>2.7839</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1794</v>
+        <v>1.1075</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7243</v>
+        <v>1.6764</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.084</v>
+        <v>-3.9738</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0901</v>
+        <v>-2.0148</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9939</v>
+        <v>-1.959</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7067</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5177</v>
+        <v>-0.5782</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1891</v>
+        <v>-0.1572</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6357</v>
+        <v>-5.5976</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4335</v>
+        <v>-0.5596</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.2022</v>
+        <v>-5.0381</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5448</v>
+        <v>-3.5263</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.982</v>
+        <v>-1.9914</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5628</v>
+        <v>-1.5349</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5221</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7444</v>
+        <v>-0.8068</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2223</v>
+        <v>0.2196</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0227</v>
+        <v>-2.9391</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2376</v>
+        <v>-1.1846</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7851</v>
+        <v>-1.7545</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0743</v>
+        <v>-0.113</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0887</v>
+        <v>0.0276</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.163</v>
+        <v>-0.1406</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.705</v>
+        <v>-2.6603</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.705</v>
+        <v>-2.6603</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.021</v>
+        <v>-5.9234</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0365</v>
+        <v>0.9184</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.0575</v>
+        <v>-6.8418</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1703</v>
+        <v>-2.1176</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7391</v>
+        <v>-1.6935</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4311</v>
+        <v>-0.4241</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7433</v>
+        <v>1.6902</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1805</v>
+        <v>0.1553</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5628</v>
+        <v>1.5349</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.9135</v>
+        <v>-3.8077</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9196</v>
+        <v>-1.8488</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9939</v>
+        <v>-1.959</v>
       </c>
       <c r="P11" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7067</v>
+        <v>-0.7718</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.206</v>
+        <v>-0.1753</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.3969</v>
+        <v>-3.3266</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3969</v>
+        <v>-3.3266</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5371</v>
+        <v>-6.5988</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7481</v>
+        <v>-2.9675</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.789</v>
+        <v>-3.6313</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2837</v>
+        <v>-2.2929</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1861</v>
+        <v>-2.1983</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0977</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1302</v>
+        <v>0.0417</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2841</v>
+        <v>-0.3585</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4142</v>
+        <v>0.4002</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4139</v>
+        <v>-2.3347</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.902</v>
+        <v>-1.8398</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5119</v>
+        <v>-0.4949</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R12" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4042</v>
+        <v>-0.4402</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7341</v>
+        <v>-0.8038</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3299</v>
+        <v>0.3636</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0132</v>
+        <v>-1.9939</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6141</v>
+        <v>-6.6626</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3705</v>
+        <v>-2.5656</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2436</v>
+        <v>-4.097</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.8024</v>
+        <v>-4.7468</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5993</v>
+        <v>-2.5434</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.203</v>
+        <v>-2.2035</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4946</v>
+        <v>-1.5231</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7081</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7885</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.3078</v>
+        <v>-3.2238</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8932</v>
+        <v>-1.8353</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4146</v>
+        <v>-1.3885</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.836</v>
+        <v>-1.8718</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R13" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6676</v>
+        <v>-0.7104</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8958</v>
+        <v>-0.9653</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2282</v>
+        <v>0.255</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3149</v>
+        <v>2.2625</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-34.8905</v>
+        <v>-34.8718</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.757999999999999</v>
+        <v>-3.394799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-33.1326</v>
+        <v>-31.477</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.9911</v>
+        <v>-18.7789</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.1401</v>
+        <v>-13.9329</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.8508</v>
+        <v>-4.846299999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>7.4718</v>
+        <v>6.827200000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4545</v>
+        <v>2.0418</v>
       </c>
       <c r="L14" t="n">
-        <v>5.0172</v>
+        <v>4.785299999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-26.4625</v>
+        <v>-25.6061</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.5946</v>
+        <v>-15.9748</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.867900000000001</v>
+        <v>-9.631600000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.295</v>
+        <v>-2.3398</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.032499999999999</v>
+        <v>-8.189</v>
       </c>
       <c r="R14" t="n">
-        <v>5.737499999999999</v>
+        <v>5.8491</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.4074</v>
+        <v>-4.7082</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.1285</v>
+        <v>-6.8265</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7214</v>
+        <v>2.1185</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.197099999999999</v>
+        <v>-9.044900000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>4.9315</v>
+        <v>4.793600000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.1286</v>
+        <v>-13.8386</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,64 +1645,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8681</v>
+        <v>7.8351</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5831</v>
+        <v>7.3503</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2849</v>
+        <v>0.4848</v>
       </c>
       <c r="G15" t="n">
-        <v>6.721</v>
+        <v>6.6422</v>
       </c>
       <c r="H15" t="n">
-        <v>3.356</v>
+        <v>3.3089</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3649</v>
+        <v>3.3333</v>
       </c>
       <c r="J15" t="n">
-        <v>8.097300000000001</v>
+        <v>7.9319</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1262</v>
+        <v>4.0179</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9711</v>
+        <v>3.9141</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3763</v>
+        <v>-1.2898</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7702</v>
+        <v>-0.709</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6061</v>
+        <v>-0.5808</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7667</v>
+        <v>0.8246</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.206</v>
+        <v>-0.2481</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9727</v>
+        <v>1.0727</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1728,64 +1728,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.422</v>
+        <v>6.3276</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5324</v>
+        <v>5.3122</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8895999999999999</v>
+        <v>1.0155</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5444</v>
+        <v>1.5351</v>
       </c>
       <c r="H16" t="n">
-        <v>1.046</v>
+        <v>1.0554</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4984</v>
+        <v>0.4798</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0122</v>
+        <v>1.9473</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9548</v>
+        <v>0.9298</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0574</v>
+        <v>1.0176</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4678</v>
+        <v>-0.4122</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0912</v>
+        <v>0.1256</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R16" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4772</v>
+        <v>0.5014</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0378</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4394</v>
+        <v>0.4918</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6298</v>
+        <v>4.5251</v>
       </c>
       <c r="W16" t="n">
-        <v>4.6298</v>
+        <v>4.5251</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1811,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7833</v>
+        <v>4.7459</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2486</v>
+        <v>4.1231</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5346</v>
+        <v>0.6229</v>
       </c>
       <c r="G17" t="n">
-        <v>4.5681</v>
+        <v>4.4993</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1097</v>
+        <v>3.0567</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4585</v>
+        <v>1.4426</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6007</v>
+        <v>4.4936</v>
       </c>
       <c r="K17" t="n">
-        <v>3.0009</v>
+        <v>2.9221</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5998</v>
+        <v>1.5715</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0326</v>
+        <v>0.0058</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1088</v>
+        <v>0.1346</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1414</v>
+        <v>-0.1289</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="R17" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2152</v>
+        <v>0.2466</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1069</v>
+        <v>0.0974</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1082</v>
+        <v>0.1492</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1894,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3975</v>
+        <v>4.3791</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5997</v>
+        <v>3.4171</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7978</v>
+        <v>0.9619</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3739</v>
+        <v>3.3248</v>
       </c>
       <c r="H18" t="n">
-        <v>0.137</v>
+        <v>0.1252</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2369</v>
+        <v>3.1996</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4003</v>
+        <v>4.278</v>
       </c>
       <c r="K18" t="n">
-        <v>0.719</v>
+        <v>0.6592</v>
       </c>
       <c r="L18" t="n">
-        <v>3.6813</v>
+        <v>3.6188</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0265</v>
+        <v>-0.9532</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.582</v>
+        <v>-0.534</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4444</v>
+        <v>-0.4192</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3351</v>
+        <v>0.3524</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3416</v>
+        <v>-0.3929</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6768</v>
+        <v>0.7453</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1977,64 +1977,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2459</v>
+        <v>4.2268</v>
       </c>
       <c r="E19" t="n">
-        <v>4.1987</v>
+        <v>4.0552</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0472</v>
+        <v>0.1716</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4077</v>
+        <v>1.384</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9432</v>
+        <v>1.9003</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5354</v>
+        <v>-0.5164</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3606</v>
+        <v>2.2808</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1754</v>
+        <v>2.0978</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1853</v>
+        <v>0.183</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9529</v>
+        <v>-0.8968</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2322</v>
+        <v>-0.1975</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7207</v>
+        <v>-0.6994</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R19" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4446</v>
+        <v>0.4806</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0965</v>
+        <v>-0.1199</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5411</v>
+        <v>0.6004</v>
       </c>
       <c r="V19" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="W19" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8507</v>
+        <v>2.8939</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7052</v>
+        <v>0.6438</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1455</v>
+        <v>2.2501</v>
       </c>
       <c r="G20" t="n">
-        <v>1.626</v>
+        <v>1.6354</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4186</v>
+        <v>-0.3953</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0446</v>
+        <v>2.0307</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1264</v>
+        <v>1.1021</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6891</v>
+        <v>-0.6915</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8155</v>
+        <v>1.7935</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4996</v>
+        <v>0.5333</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2705</v>
+        <v>0.2961</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2291</v>
+        <v>0.2372</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R20" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S20" t="n">
-        <v>0.605</v>
+        <v>0.6268</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1917</v>
+        <v>-0.2243</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7967</v>
+        <v>0.8511</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3901</v>
+        <v>0.3978</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3901</v>
+        <v>0.3978</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.1743</v>
+        <v>2.1946</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9365</v>
+        <v>2.8184</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7623</v>
+        <v>-0.6238</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3537</v>
+        <v>-0.3291</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3569</v>
+        <v>0.3639</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7106</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1402</v>
+        <v>1.0998</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2447</v>
+        <v>1.212</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1045</v>
+        <v>-0.1122</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4939</v>
+        <v>-1.4289</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8878</v>
+        <v>-0.8481</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6061</v>
+        <v>-0.5808</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2165</v>
+        <v>0.2256</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3677</v>
+        <v>-0.4096</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.6352</v>
       </c>
       <c r="V21" t="n">
-        <v>1.623</v>
+        <v>1.5962</v>
       </c>
       <c r="W21" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.7511</v>
+        <v>1.8214</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0432</v>
+        <v>1.9532</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2921</v>
+        <v>-0.1318</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2538</v>
+        <v>0.2621</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5703</v>
+        <v>0.5676</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3166</v>
+        <v>-0.3055</v>
       </c>
       <c r="J22" t="n">
-        <v>0.789</v>
+        <v>0.75</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6408</v>
+        <v>0.6035</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1482</v>
+        <v>0.1464</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5353</v>
+        <v>-0.4878</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0359</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4648</v>
+        <v>-0.4519</v>
       </c>
       <c r="P22" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1892</v>
+        <v>1.2256</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4016</v>
+        <v>0.3731</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7876</v>
+        <v>0.8525</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W22" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3206</v>
+        <v>1.3424</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0033</v>
+        <v>-0.0026</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3173</v>
+        <v>1.345</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7091</v>
+        <v>0.7115</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3487</v>
+        <v>0.3518</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3604</v>
+        <v>0.3597</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0712</v>
+        <v>0.0698</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0341</v>
+        <v>0.0332</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6379</v>
+        <v>0.6417</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3146</v>
+        <v>0.3186</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3234</v>
+        <v>0.3231</v>
       </c>
       <c r="P23" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1526</v>
+        <v>0.163</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0678</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2204</v>
+        <v>0.2354</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.17</v>
+        <v>1.1736</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9055</v>
+        <v>0.7369</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2645</v>
+        <v>0.4366</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.881</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6385</v>
+        <v>-0.634</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2425</v>
+        <v>-0.2323</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4601</v>
+        <v>0.4055</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0653</v>
+        <v>-0.1045</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5254</v>
+        <v>0.51</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.341</v>
+        <v>-1.2718</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5732</v>
+        <v>-0.5295</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7678</v>
+        <v>-0.7423</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2673</v>
+        <v>0.28</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3416</v>
+        <v>-0.3929</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6089</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>2.0132</v>
+        <v>1.9939</v>
       </c>
       <c r="W24" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2365</v>
+        <v>0.2778</v>
       </c>
       <c r="E25" t="n">
-        <v>0.749</v>
+        <v>0.645</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5125</v>
+        <v>-0.3672</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4103</v>
+        <v>-0.4047</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5669</v>
+        <v>1.5503</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9772</v>
+        <v>-1.9551</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1306</v>
+        <v>-0.1675</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4493</v>
+        <v>1.4112</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5798</v>
+        <v>-1.5788</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2797</v>
+        <v>-0.2372</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1176</v>
+        <v>0.1391</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3973</v>
+        <v>-0.3763</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4173</v>
+        <v>0.4485</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3534</v>
+        <v>-0.3859</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7706</v>
+        <v>0.8344</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2558,67 +2558,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.1819</v>
+        <v>-1.1764</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6274</v>
+        <v>0.4247</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8093</v>
+        <v>-1.6011</v>
       </c>
       <c r="G26" t="n">
-        <v>0.432</v>
+        <v>0.3848</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7628</v>
+        <v>2.682</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.3308</v>
+        <v>-2.2972</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5351</v>
+        <v>1.415</v>
       </c>
       <c r="K26" t="n">
-        <v>3.0038</v>
+        <v>2.884</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.4687</v>
+        <v>-1.469</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1031</v>
+        <v>-1.0302</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.241</v>
+        <v>-0.2019</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8621</v>
+        <v>-0.8282</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4681</v>
+        <v>0.5029</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3012</v>
+        <v>-0.3525</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7693</v>
+        <v>0.8554</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
       <c r="W26" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.164</v>
+        <v>-2.1282</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2641,67 +2641,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>36.0381</v>
+        <v>36.04179999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>33.1326</v>
+        <v>31.4773</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9052</v>
+        <v>4.564500000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>18.991</v>
+        <v>18.779</v>
       </c>
       <c r="H27" t="n">
-        <v>14.1404</v>
+        <v>13.9328</v>
       </c>
       <c r="I27" t="n">
-        <v>4.8506</v>
+        <v>4.846200000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>26.4625</v>
+        <v>25.6063</v>
       </c>
       <c r="K27" t="n">
-        <v>16.5946</v>
+        <v>15.9747</v>
       </c>
       <c r="L27" t="n">
-        <v>9.868099999999998</v>
+        <v>9.631500000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.4716</v>
+        <v>-6.8271</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.4542</v>
+        <v>-2.0419</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.017200000000001</v>
+        <v>-4.7853</v>
       </c>
       <c r="P27" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5.7375</v>
+        <v>-5.849299999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>8.032499999999999</v>
+        <v>8.1889</v>
       </c>
       <c r="S27" t="n">
-        <v>5.554799999999998</v>
+        <v>5.878000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.7212</v>
+        <v>-2.1184</v>
       </c>
       <c r="U27" t="n">
-        <v>7.2759</v>
+        <v>7.996300000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>9.197100000000001</v>
+        <v>9.045</v>
       </c>
       <c r="W27" t="n">
-        <v>14.1286</v>
+        <v>13.8386</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.931600000000001</v>
+        <v>-4.7936</v>
       </c>
       <c r="Y27" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105351_W2.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105351_W2.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.837</v>
+        <v>0.8723</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7271</v>
+        <v>3.8288</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8901</v>
+        <v>-2.9564</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1315</v>
+        <v>2.1378</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1144</v>
+        <v>0.1165</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0171</v>
+        <v>2.0213</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4751</v>
+        <v>4.5004</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2863</v>
+        <v>2.3136</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1889</v>
+        <v>2.1868</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3436</v>
+        <v>-2.3626</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.1718</v>
+        <v>-2.197</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1718</v>
+        <v>-0.1655</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.7019</v>
+        <v>-0.6962</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4583</v>
+        <v>-0.4279</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6423</v>
+        <v>-0.583</v>
       </c>
       <c r="U2" t="n">
-        <v>0.184</v>
+        <v>0.155</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,58 +653,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1315</v>
+        <v>0.1354</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4355</v>
+        <v>0.4669</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.304</v>
+        <v>-0.3315</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0772</v>
+        <v>0.0838</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6242</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5403</v>
+        <v>-0.5404</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8701</v>
+        <v>0.8796</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.8061</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0732</v>
+        <v>0.0736</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.793</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1795</v>
+        <v>-0.1819</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6135</v>
+        <v>-0.614</v>
       </c>
       <c r="P3" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1796</v>
+        <v>-0.1805</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4346</v>
+        <v>-0.4128</v>
       </c>
       <c r="U3" t="n">
-        <v>0.255</v>
+        <v>0.2323</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -736,67 +736,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.607</v>
+        <v>-0.6176</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5904</v>
+        <v>-0.5874</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0165</v>
+        <v>-0.0302</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7693</v>
+        <v>-1.7885</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1231</v>
+        <v>-1.1354</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6462</v>
+        <v>-0.6531</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.5988</v>
+        <v>-1.6159</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7911</v>
+        <v>-0.7996</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1705</v>
+        <v>-0.1726</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3321</v>
+        <v>-0.3359</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1615</v>
+        <v>0.1633</v>
       </c>
       <c r="P4" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0014</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0558</v>
+        <v>-0.0431</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0543</v>
+        <v>0.0516</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9298</v>
+        <v>0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1893</v>
+        <v>-1.1886</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5258</v>
+        <v>0.5874</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7151</v>
+        <v>-1.776</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.671</v>
+        <v>-0.6796</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0307</v>
+        <v>-1.043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3597</v>
+        <v>0.3633</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2085</v>
+        <v>1.2112</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1494</v>
+        <v>0.1511</v>
       </c>
       <c r="L5" t="n">
-        <v>1.059</v>
+        <v>1.0601</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8795</v>
+        <v>-1.8908</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1802</v>
+        <v>-1.1941</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6994</v>
+        <v>-0.6967</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1561</v>
+        <v>-0.1335</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6826</v>
+        <v>-0.6238</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5266</v>
+        <v>0.4903</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3546</v>
+        <v>-1.3722</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8798</v>
+        <v>0.9694</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2344</v>
+        <v>-2.3417</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6735</v>
+        <v>-0.6766</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.368</v>
+        <v>-0.3731</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3055</v>
+        <v>-0.3035</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7311</v>
+        <v>1.7459</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6603</v>
+        <v>1.6793</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0708</v>
+        <v>0.0667</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4045</v>
+        <v>-2.4226</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0282</v>
+        <v>-2.0524</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3763</v>
+        <v>-0.3702</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3189</v>
+        <v>-0.3201</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8512</v>
+        <v>-0.7765</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5323</v>
+        <v>0.4564</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7898</v>
+        <v>-1.7859</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0723</v>
+        <v>-1.0405</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7175</v>
+        <v>-0.7454</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.773</v>
+        <v>-1.7921</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8921</v>
+        <v>-0.9022</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8809</v>
+        <v>-0.89</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5665</v>
+        <v>-0.5823</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7081</v>
+        <v>-0.7156</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1415</v>
+        <v>0.1333</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2064</v>
+        <v>-1.2098</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.184</v>
+        <v>-0.1865</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0224</v>
+        <v>-1.0233</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4848</v>
+        <v>-0.458</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5057</v>
+        <v>-0.4582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.021</v>
+        <v>0.0002</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1068,67 +1068,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8227</v>
+        <v>-2.856</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2606</v>
+        <v>-2.2444</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5621</v>
+        <v>-0.6116</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2273</v>
+        <v>-2.256</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9169</v>
+        <v>-1.9387</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3104</v>
+        <v>-0.3174</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6978</v>
+        <v>-1.7197</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7413</v>
+        <v>-0.7492</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9565</v>
+        <v>-0.9705</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5295</v>
+        <v>-0.5364</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1757</v>
+        <v>-1.1895</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6462</v>
+        <v>0.6531</v>
       </c>
       <c r="P8" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.163</v>
+        <v>-0.1548</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5628</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3998</v>
+        <v>0.3699</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6664</v>
+        <v>-0.6772</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1151,64 +1151,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2945</v>
+        <v>-3.2668</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1346</v>
+        <v>0.2279</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4291</v>
+        <v>-3.4947</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1899</v>
+        <v>-1.2092</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9171</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2826</v>
+        <v>-0.2921</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7839</v>
+        <v>2.793</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1075</v>
+        <v>1.1213</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6764</v>
+        <v>1.6717</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.9738</v>
+        <v>-4.0022</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0148</v>
+        <v>-2.0384</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.959</v>
+        <v>-1.9638</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7157</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5782</v>
+        <v>-0.527</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1572</v>
+        <v>-0.1887</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1234,67 +1234,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5976</v>
+        <v>-5.6117</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5596</v>
+        <v>-0.5077</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.0381</v>
+        <v>-5.104</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5263</v>
+        <v>-3.5509</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9914</v>
+        <v>-2.0125</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5349</v>
+        <v>-1.5384</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.593</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8068</v>
+        <v>-0.8137</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2196</v>
+        <v>0.2208</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9391</v>
+        <v>-2.9579</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1846</v>
+        <v>-1.1988</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7545</v>
+        <v>-1.7591</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.113</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0276</v>
+        <v>0.0853</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1406</v>
+        <v>-0.163</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6603</v>
+        <v>-2.6793</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6603</v>
+        <v>-2.6793</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1317,67 +1317,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9234</v>
+        <v>-5.9548</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9184</v>
+        <v>0.9777</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.8418</v>
+        <v>-6.9325</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1176</v>
+        <v>-2.1383</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6935</v>
+        <v>-1.7129</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4241</v>
+        <v>-0.4254</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6902</v>
+        <v>1.696</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1553</v>
+        <v>0.1576</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5349</v>
+        <v>1.5384</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.8077</v>
+        <v>-3.8343</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8488</v>
+        <v>-1.8705</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.959</v>
+        <v>-1.9638</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9242</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7718</v>
+        <v>-0.7183</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1753</v>
+        <v>-0.2059</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.3266</v>
+        <v>-3.3565</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3266</v>
+        <v>-3.3565</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5988</v>
+        <v>-6.5852</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9675</v>
+        <v>-2.8881</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6313</v>
+        <v>-3.697</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2929</v>
+        <v>-2.3158</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1983</v>
+        <v>-2.2215</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0417</v>
+        <v>0.0375</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3585</v>
+        <v>-0.3603</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4002</v>
+        <v>0.3978</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3347</v>
+        <v>-2.3532</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8398</v>
+        <v>-1.8612</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4949</v>
+        <v>-0.4921</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8718</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4402</v>
+        <v>-0.4107</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8038</v>
+        <v>-0.7462</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3636</v>
+        <v>0.3355</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9939</v>
+        <v>-2.0021</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6626</v>
+        <v>-6.6571</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5656</v>
+        <v>-2.4982</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.097</v>
+        <v>-4.1588</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.7468</v>
+        <v>-4.8005</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5434</v>
+        <v>-2.5721</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.2035</v>
+        <v>-2.2284</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5231</v>
+        <v>-1.5528</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7081</v>
+        <v>-0.7156</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2238</v>
+        <v>-3.2477</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8353</v>
+        <v>-1.8565</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3885</v>
+        <v>-1.3912</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8718</v>
+        <v>-1.8566</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3397</v>
+        <v>-2.3207</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7104</v>
+        <v>-0.6772</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9653</v>
+        <v>-0.9095</v>
       </c>
       <c r="U13" t="n">
-        <v>0.255</v>
+        <v>0.2323</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2625</v>
+        <v>2.2848</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1566,67 +1566,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-34.8718</v>
+        <v>-34.8882</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.394799999999999</v>
+        <v>-2.708200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-31.477</v>
+        <v>-32.1798</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.7789</v>
+        <v>-18.9859</v>
       </c>
       <c r="H14" t="n">
-        <v>-13.9329</v>
+        <v>-14.0878</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.846299999999999</v>
+        <v>-4.8984</v>
       </c>
       <c r="J14" t="n">
-        <v>6.827200000000001</v>
+        <v>6.799900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0418</v>
+        <v>2.075</v>
       </c>
       <c r="L14" t="n">
-        <v>4.785299999999999</v>
+        <v>4.725099999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.6061</v>
+        <v>-25.786</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.9748</v>
+        <v>-16.1627</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.631600000000001</v>
+        <v>-9.6233</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.3398</v>
+        <v>-2.3208</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.189</v>
+        <v>-8.1225</v>
       </c>
       <c r="R14" t="n">
-        <v>5.8491</v>
+        <v>5.801600000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.7082</v>
+        <v>-4.4719</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.8265</v>
+        <v>-6.2378</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1185</v>
+        <v>1.7659</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.044900000000002</v>
+        <v>-9.109500000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>4.793600000000001</v>
+        <v>4.852200000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.8386</v>
+        <v>-13.9617</v>
       </c>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1645,64 +1645,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8351</v>
+        <v>7.8524</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3503</v>
+        <v>7.46</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4848</v>
+        <v>0.3924</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6422</v>
+        <v>6.7007</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3089</v>
+        <v>3.3456</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3333</v>
+        <v>3.3551</v>
       </c>
       <c r="J15" t="n">
-        <v>7.9319</v>
+        <v>7.9938</v>
       </c>
       <c r="K15" t="n">
-        <v>4.0179</v>
+        <v>4.0639</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9141</v>
+        <v>3.9299</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2898</v>
+        <v>-1.2931</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.709</v>
+        <v>-0.7183</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5808</v>
+        <v>-0.5748</v>
       </c>
       <c r="P15" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8246</v>
+        <v>0.7783</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2481</v>
+        <v>-0.211</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0727</v>
+        <v>0.9893</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1343</v>
+        <v>0.1413</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1728,64 +1728,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3276</v>
+        <v>6.3635</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3122</v>
+        <v>5.3952</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0155</v>
+        <v>0.9683</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5351</v>
+        <v>1.5424</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0554</v>
+        <v>1.0664</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4798</v>
+        <v>0.476</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9473</v>
+        <v>1.9498</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9298</v>
+        <v>0.9404</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0176</v>
+        <v>1.0094</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4122</v>
+        <v>-0.4074</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1256</v>
+        <v>0.126</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5335</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9359</v>
+        <v>0.9283</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5014</v>
+        <v>0.4836</v>
       </c>
       <c r="T16" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0362</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4918</v>
+        <v>0.4474</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5251</v>
+        <v>4.5695</v>
       </c>
       <c r="W16" t="n">
-        <v>4.5251</v>
+        <v>4.5695</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1811,58 +1811,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7459</v>
+        <v>4.7614</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1231</v>
+        <v>4.1739</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6229</v>
+        <v>0.5875</v>
       </c>
       <c r="G17" t="n">
-        <v>4.4993</v>
+        <v>4.5419</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0567</v>
+        <v>3.0909</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4426</v>
+        <v>1.451</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4936</v>
+        <v>4.5307</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9221</v>
+        <v>2.9555</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5715</v>
+        <v>1.5752</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0058</v>
+        <v>0.0112</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1346</v>
+        <v>0.1353</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1289</v>
+        <v>-0.1241</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2466</v>
+        <v>0.2195</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0974</v>
+        <v>0.1073</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1492</v>
+        <v>0.1122</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1894,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3791</v>
+        <v>4.3798</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4171</v>
+        <v>3.4838</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9619</v>
+        <v>0.896</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3248</v>
+        <v>3.3439</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1252</v>
+        <v>0.1269</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1996</v>
+        <v>3.2171</v>
       </c>
       <c r="J18" t="n">
-        <v>4.278</v>
+        <v>4.2965</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6592</v>
+        <v>0.6679</v>
       </c>
       <c r="L18" t="n">
-        <v>3.6188</v>
+        <v>3.6286</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9532</v>
+        <v>-0.9526</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.534</v>
+        <v>-0.541</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4192</v>
+        <v>-0.4116</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3524</v>
+        <v>0.3396</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3929</v>
+        <v>-0.3486</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7453</v>
+        <v>0.6882</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1977,64 +1977,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2268</v>
+        <v>4.2362</v>
       </c>
       <c r="E19" t="n">
-        <v>4.0552</v>
+        <v>4.1186</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1716</v>
+        <v>0.1175</v>
       </c>
       <c r="G19" t="n">
-        <v>1.384</v>
+        <v>1.4091</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9003</v>
+        <v>1.9219</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5164</v>
+        <v>-0.5128</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2808</v>
+        <v>2.3063</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0978</v>
+        <v>2.1224</v>
       </c>
       <c r="L19" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8968</v>
+        <v>-0.8972</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1975</v>
+        <v>-0.2005</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6994</v>
+        <v>-0.6967</v>
       </c>
       <c r="P19" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4806</v>
+        <v>0.4515</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1199</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6004</v>
+        <v>0.5506</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8939</v>
+        <v>2.8855</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6438</v>
+        <v>0.6761</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2501</v>
+        <v>2.2094</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6354</v>
+        <v>1.6464</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3953</v>
+        <v>-0.4002</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0307</v>
+        <v>2.0466</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1021</v>
+        <v>1.104</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6915</v>
+        <v>-0.6988</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7935</v>
+        <v>1.8028</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5333</v>
+        <v>0.5424</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2961</v>
+        <v>0.2986</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2372</v>
+        <v>0.2438</v>
       </c>
       <c r="P20" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6268</v>
+        <v>0.6125</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2243</v>
+        <v>-0.1959</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8511</v>
+        <v>0.8084</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3978</v>
+        <v>0.3945</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3978</v>
+        <v>0.3945</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.1946</v>
+        <v>2.1985</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8184</v>
+        <v>2.8777</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6238</v>
+        <v>-0.6792</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3291</v>
+        <v>-0.3245</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3639</v>
+        <v>0.3676</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.6921</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0998</v>
+        <v>1.1086</v>
       </c>
       <c r="K21" t="n">
-        <v>1.212</v>
+        <v>1.2259</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1122</v>
+        <v>-0.1173</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4289</v>
+        <v>-1.4331</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8481</v>
+        <v>-0.8583</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5808</v>
+        <v>-0.5748</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2256</v>
+        <v>0.2192</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4096</v>
+        <v>-0.3743</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6352</v>
+        <v>0.5935</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5962</v>
+        <v>1.6076</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5321</v>
+        <v>-0.5359</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8214</v>
+        <v>1.7966</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9532</v>
+        <v>2.0014</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1318</v>
+        <v>-0.2049</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2621</v>
+        <v>0.2703</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5676</v>
+        <v>0.5738</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3055</v>
+        <v>-0.3035</v>
       </c>
       <c r="J22" t="n">
-        <v>0.75</v>
+        <v>0.7582</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6035</v>
+        <v>0.611</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1464</v>
+        <v>0.1472</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4878</v>
+        <v>-0.4879</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0359</v>
+        <v>-0.0372</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4519</v>
+        <v>-0.4507</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2256</v>
+        <v>1.2035</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3731</v>
+        <v>0.4036</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8525</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0641</v>
+        <v>1.0717</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3424</v>
+        <v>1.3378</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0026</v>
+        <v>0.0016</v>
       </c>
       <c r="F23" t="n">
-        <v>1.345</v>
+        <v>1.3362</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7115</v>
+        <v>0.7188</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3518</v>
+        <v>0.3555</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3597</v>
+        <v>0.3633</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0698</v>
+        <v>0.0704</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0332</v>
+        <v>0.0336</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0366</v>
+        <v>0.0368</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6417</v>
+        <v>0.6484</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3186</v>
+        <v>0.3219</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3231</v>
+        <v>0.3265</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4679</v>
+        <v>0.4641</v>
       </c>
       <c r="S23" t="n">
-        <v>0.163</v>
+        <v>0.1548</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0688</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2354</v>
+        <v>0.2236</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2392,67 +2392,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1736</v>
+        <v>1.17</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7369</v>
+        <v>0.806</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4366</v>
+        <v>0.364</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.8709</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.634</v>
+        <v>-0.641</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2323</v>
+        <v>-0.2299</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4055</v>
+        <v>0.4036</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1045</v>
+        <v>-0.1046</v>
       </c>
       <c r="L24" t="n">
-        <v>0.51</v>
+        <v>0.5082</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2718</v>
+        <v>-1.2745</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5295</v>
+        <v>-0.5364</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7423</v>
+        <v>-0.7381</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.4038</v>
+        <v>-1.3924</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1699</v>
+        <v>1.1604</v>
       </c>
       <c r="S24" t="n">
-        <v>0.28</v>
+        <v>0.2708</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3929</v>
+        <v>-0.3486</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6194</v>
       </c>
       <c r="V24" t="n">
-        <v>1.9939</v>
+        <v>2.0021</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2778</v>
+        <v>0.2569</v>
       </c>
       <c r="E25" t="n">
-        <v>0.645</v>
+        <v>0.6854</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3672</v>
+        <v>-0.4285</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4047</v>
+        <v>-0.3987</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5503</v>
+        <v>1.5674</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9551</v>
+        <v>-1.9661</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1675</v>
+        <v>-0.1686</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4112</v>
+        <v>1.4274</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5788</v>
+        <v>-1.5959</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2372</v>
+        <v>-0.2302</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1391</v>
+        <v>0.14</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3763</v>
+        <v>-0.3702</v>
       </c>
       <c r="P25" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4485</v>
+        <v>0.4236</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3859</v>
+        <v>-0.3591</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8344</v>
+        <v>0.7827</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1984</v>
+        <v>1.213</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.1984</v>
+        <v>-1.213</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2558,67 +2558,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.1764</v>
+        <v>-1.19</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4247</v>
+        <v>0.5003</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6011</v>
+        <v>-1.6903</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3848</v>
+        <v>0.4065</v>
       </c>
       <c r="H26" t="n">
-        <v>2.682</v>
+        <v>2.713</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.2972</v>
+        <v>-2.3064</v>
       </c>
       <c r="J26" t="n">
-        <v>1.415</v>
+        <v>1.4326</v>
       </c>
       <c r="K26" t="n">
-        <v>2.884</v>
+        <v>2.9181</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.469</v>
+        <v>-1.4856</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.0302</v>
+        <v>-1.026</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2019</v>
+        <v>-0.2052</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.8282</v>
+        <v>-0.8209</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.4679</v>
+        <v>-0.4641</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5029</v>
+        <v>0.4752</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3525</v>
+        <v>-0.3078</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8554</v>
+        <v>0.7829</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5321</v>
+        <v>0.5359</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.1282</v>
+        <v>-2.1434</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2641,67 +2641,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>36.04179999999999</v>
+        <v>36.04860000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>31.4773</v>
+        <v>32.18000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>4.564500000000001</v>
+        <v>3.8684</v>
       </c>
       <c r="G27" t="n">
-        <v>18.779</v>
+        <v>18.9859</v>
       </c>
       <c r="H27" t="n">
-        <v>13.9328</v>
+        <v>14.0878</v>
       </c>
       <c r="I27" t="n">
-        <v>4.846200000000001</v>
+        <v>4.8983</v>
       </c>
       <c r="J27" t="n">
-        <v>25.6063</v>
+        <v>25.7859</v>
       </c>
       <c r="K27" t="n">
-        <v>15.9747</v>
+        <v>16.1627</v>
       </c>
       <c r="L27" t="n">
-        <v>9.631500000000001</v>
+        <v>9.6233</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.8271</v>
+        <v>-6.8</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.0419</v>
+        <v>-2.0751</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.7853</v>
+        <v>-4.725099999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>2.3397</v>
+        <v>2.3207</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5.849299999999999</v>
+        <v>-5.8018</v>
       </c>
       <c r="R27" t="n">
-        <v>8.1889</v>
+        <v>8.122400000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>5.878000000000001</v>
+        <v>5.6321</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.1184</v>
+        <v>-1.7661</v>
       </c>
       <c r="U27" t="n">
-        <v>7.996300000000001</v>
+        <v>7.398099999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>9.045</v>
+        <v>9.109500000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>13.8386</v>
+        <v>13.9616</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.7936</v>
+        <v>-4.8521</v>
       </c>
       <c r="Y27" t="inlineStr"/>
     </row>
